--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2367,22 +2367,62 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sheff Utd</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2425,22 +2425,62 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>19</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2483,22 +2483,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>15</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2541,22 +2541,62 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7</v>
+      </c>
+      <c r="N37" t="n">
+        <v>13</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2599,22 +2599,62 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="n">
+        <v>19</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2657,22 +2657,62 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2715,22 +2715,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M40" t="n">
+        <v>8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2773,40 +2773,120 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M41" t="n">
+        <v>16</v>
+      </c>
+      <c r="N41" t="n">
+        <v>12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>24</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2889,22 +2889,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M43" t="n">
+        <v>8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>20</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -2947,22 +2947,62 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Charlton</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M44" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" t="n">
+        <v>12</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -3005,40 +3005,120 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>18</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M46" t="n">
+        <v>9</v>
+      </c>
+      <c r="N46" t="n">
+        <v>20</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>

--- a/new-stats/sheffield-wednesday-fc.xlsx
+++ b/new-stats/sheffield-wednesday-fc.xlsx
@@ -3121,22 +3121,62 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sheff Wed</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11</v>
+      </c>
+      <c r="N47" t="n">
+        <v>13</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5</v>
+      </c>
+      <c r="P47" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
